--- a/outputs/evaluation/decision/v1/CF_M08/run_2/CF_M08_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_2/CF_M08_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,37 +471,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_07, Scalability</t>
+          <t>C_02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_03, AU_06, AU_15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12g. Expansion or Growth Requirements; Scalability</t>
+          <t>11a. Ease of Use Requirements</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>System Service; Next.js; React</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -515,157 +515,407 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6187</v>
+        <v>0.7219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_05, Maintainability</t>
+          <t>R_03, R_04, R_05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_03, AU_06, AU_14, AU_18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14a. Maintenance Requirements; Maintainability</t>
+          <t>The system must allow registering new users to the system.; The system must be able to authenticate existing users through email.; The system must allow users to log out.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Component-Based</t>
+          <t>System Service; Next.js; Brevo; AU_18</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.7336</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects... When the subject's state changes, it automatically notifies all its observers, allowing them to react appropriately.</t>
+          <t>Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_06, Adaptability</t>
+          <t>R_07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_03, AU_06, AU_10, AU_19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14c. Adaptability Requirements; Adaptability</t>
+          <t>The system must be able to save all images of all products/users in the system.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Observer Pattern</t>
+          <t>System Service; Next.js; Amazon S3; AU_19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.5961</v>
+        <v>0.5879</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is used generally to manage shared resources, such as configurations, logs or database connections, where having multiple instances could lead to inconsistent states or inefficient use of resources.</t>
+          <t>Integra con Stripe para manejar pagos y suscripciones.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C_04, Robustness</t>
+          <t>R_14, R_15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_03, AU_06, AU_11, AU_20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Every route must have an associated budget (which can be 0) which the user must be able to pay through the use of the system when returning the product.; The system must have an affiliation/plans system for companies that want to have certain advantages (it has three plans: free, basic, and premium).</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>System Service; Next.js; Stripe; AU_20</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6136</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C_07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AU_03, AU_06, AU_12, AU_21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12g. Expansion or Growth Requirements</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>System Service; Next.js; Google Analytics; AU_21</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CF_M08_AD06</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6062</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C_04</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AU_03, AU_06, AU_13, AU_22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12e. Robustness or Fault Tolerance Requirements</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>System Service; Next.js; Sentry; AU_22</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6098</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD_10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C_02</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>P_02, AU_15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>11a. Ease of Use Requirements</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Component-Based; React</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CF_M08_AD09</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7141999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AD_11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>El patrón Observer establece una relación de uno a muchos entre objetos, donde un objeto conocido como el sujeto mantiene una lista de otros objetos llamados observadores.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C_04</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>12e. Robustness or Fault Tolerance Requirements</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Observer Pattern</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CF_M08_AD13</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>It is generally used for manage shared resources, such as configurations, records or connections to databases data, where having multiple instances could lead to inconsistent states or usage resource inefficient.</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5978</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AD_12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>El patrón Singleton asegura que una clase tenga solo una instancia y proporciona un punto de acceso global a esa instancia. Se utiliza generalmente para gestionar recursos compartidos [...] se ha empleado, por ejemplo, para gestionar la instancia de PrismaClient</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>P_04, AU_08</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>12e. Robustness or Fault Tolerance Requirements; Robustness</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Singleton Pattern</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CF_M08_AD10</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>It is designed to simplify access and database management</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6387</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>14a. Maintenance Requirements</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Singleton Pattern; Prisma</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CF_M08_AD13</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>It is generally used for manage shared resources, such as configurations, records or connections to databases data, where having multiple instances could lead to inconsistent states or usage resource inefficient.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7391</v>
       </c>
     </row>
   </sheetData>
